--- a/2026/PICHINCHA/Mayo/PICHINCHA-Mayo.xlsx
+++ b/2026/PICHINCHA/Mayo/PICHINCHA-Mayo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PICHINCHA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\PICHINCHA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F99FCCD-1C20-4D81-9015-4BA109CB9019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9547B7DC-66C4-4874-88D8-657F50D39F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -22,11 +22,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
   <si>
     <t>UF</t>
   </si>
@@ -247,24 +252,9 @@
     <t xml:space="preserve">FLOW </t>
   </si>
   <si>
-    <t>AYSA VTO MES DE AGOSTO 2025</t>
-  </si>
-  <si>
-    <t>AYSA CARGO POR AVISO DE MORA</t>
-  </si>
-  <si>
-    <t>METROGAS VTO 17/03</t>
-  </si>
-  <si>
-    <t>METROGAS VTO 17/04</t>
-  </si>
-  <si>
     <t>SEBASTIAN</t>
   </si>
   <si>
-    <t>Recuperacion de intereses por pago fuera de termino a administracion - Desde enero 25 a dia de la fecha - Debido a que la caja inicial pertenece a la administracion</t>
-  </si>
-  <si>
     <t>Vto. 18/06</t>
   </si>
   <si>
@@ -272,6 +262,15 @@
   </si>
   <si>
     <t>MAYO</t>
+  </si>
+  <si>
+    <t>Recuperacion de intereses por pago fuera de termino a administracion - Mes de abril - Debido a que la caja inicial pertenece a la administracion</t>
+  </si>
+  <si>
+    <t>TSG</t>
+  </si>
+  <si>
+    <t>METROGAS</t>
   </si>
 </sst>
 </file>
@@ -284,7 +283,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,13 +392,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1119,7 +1111,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1402,7 +1394,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1481,9 +1472,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1521,9 +1512,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1556,9 +1547,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1591,9 +1599,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1771,22 +1796,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1794,27 +1819,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1822,13 +1847,13 @@
       <c r="C7" s="67"/>
       <c r="D7" s="67"/>
       <c r="E7" s="24" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F7" s="109" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1836,12 +1861,12 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
@@ -1853,29 +1878,25 @@
       </c>
       <c r="F11" s="129"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="51" t="s">
-        <v>73</v>
-      </c>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
       <c r="B12" s="50"/>
-      <c r="C12" s="128">
-        <v>21891.25</v>
-      </c>
+      <c r="C12" s="128"/>
       <c r="D12" s="5"/>
       <c r="E12" s="55" t="s">
         <v>42</v>
       </c>
       <c r="F12" s="56">
-        <v>-94900.571369267185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-251627.60024926736</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="50"/>
-      <c r="C13" s="152">
-        <v>20509.21</v>
+      <c r="C13" s="128">
+        <v>20951.11</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="57" t="s">
@@ -1883,16 +1904,16 @@
       </c>
       <c r="F13" s="127">
         <f>'prorrateo '!F10</f>
-        <v>629788.98111999989</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="51" t="s">
-        <v>74</v>
+        <v>417915.47400000005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="121" t="s">
+        <v>78</v>
       </c>
       <c r="B14" s="50"/>
-      <c r="C14" s="128">
-        <v>15666.16</v>
+      <c r="C14" s="117">
+        <v>22920</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="57" t="s">
@@ -1900,31 +1921,31 @@
       </c>
       <c r="F14" s="127">
         <f>-(C37)</f>
-        <v>-687250.11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>-520227.48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="121" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="122"/>
-      <c r="C15" s="152">
+      <c r="C15" s="128">
         <v>119977</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="131" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" s="132">
-        <v>-98883.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="121" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C16" s="79">
         <v>42700</v>
@@ -1936,69 +1957,65 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="121" t="s">
         <v>72</v>
       </c>
       <c r="B17" s="50"/>
       <c r="C17" s="79">
-        <v>164351.88</v>
+        <v>92365.55</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="131"/>
       <c r="F17" s="132"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="121" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="122"/>
       <c r="C18" s="117">
-        <v>24175.95</v>
+        <v>0</v>
       </c>
       <c r="E18" s="57"/>
       <c r="F18" s="58"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="121" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B19" s="122"/>
       <c r="C19" s="117">
-        <v>95246.25</v>
+        <v>125424.07</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="57"/>
       <c r="F19" s="58"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="121" t="s">
-        <v>76</v>
-      </c>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="121"/>
       <c r="B20" s="122"/>
-      <c r="C20" s="117">
-        <v>86842.66</v>
-      </c>
+      <c r="C20" s="117"/>
       <c r="E20" s="57"/>
       <c r="F20" s="58"/>
       <c r="H20" s="106"/>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="123"/>
       <c r="B21" s="124"/>
       <c r="C21" s="86">
         <f>SUM(C12:C20)</f>
-        <v>591360.36</v>
+        <v>424337.73</v>
       </c>
       <c r="E21" s="59" t="s">
         <v>43</v>
       </c>
       <c r="F21" s="119">
         <f>SUM(F12:F20)</f>
-        <v>-251245.26024926727</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-353939.60624926729</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="125" t="s">
         <v>21</v>
       </c>
@@ -2008,7 +2025,7 @@
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="121" t="s">
         <v>63</v>
       </c>
@@ -2020,7 +2037,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="121" t="s">
         <v>69</v>
       </c>
@@ -2032,7 +2049,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>71</v>
       </c>
@@ -2042,7 +2059,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="32"/>
       <c r="B26" s="33"/>
       <c r="C26" s="107">
@@ -2054,20 +2071,20 @@
       <c r="F26" s="54"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="47"/>
       <c r="C27" s="48">
         <f>+C26+C21</f>
-        <v>687250.11</v>
+        <v>520227.48</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
         <v>24</v>
       </c>
@@ -2076,18 +2093,18 @@
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43"/>
       <c r="B30" s="29"/>
       <c r="C30" s="53"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="51"/>
       <c r="B31" s="50"/>
       <c r="C31" s="52">
@@ -2095,7 +2112,7 @@
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60"/>
       <c r="B32" s="61"/>
       <c r="C32" s="52">
@@ -2103,19 +2120,19 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="77"/>
       <c r="B33" s="78"/>
       <c r="C33" s="80"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="77"/>
       <c r="B34" s="84"/>
       <c r="C34" s="85"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="77"/>
       <c r="B35" s="83"/>
       <c r="C35" s="80">
@@ -2123,7 +2140,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="62" t="s">
         <v>23</v>
       </c>
@@ -2133,98 +2150,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>54</v>
       </c>
       <c r="C37" s="52">
         <f>C27-C25</f>
-        <v>687250.11</v>
+        <v>520227.48</v>
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C38" s="76">
         <f>+C27</f>
-        <v>687250.11</v>
+        <v>520227.48</v>
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="62" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="63"/>
       <c r="C39" s="64">
         <f>+C27+C36</f>
-        <v>687250.11</v>
+        <v>520227.48</v>
       </c>
       <c r="E39" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B46" s="130"/>
       <c r="C46" s="130"/>
       <c r="D46" s="130"/>
       <c r="E46" s="130"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B47" s="130"/>
       <c r="C47" s="130"/>
       <c r="D47" s="130"/>
       <c r="E47" s="130"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="130"/>
       <c r="C48" s="130"/>
       <c r="D48" s="130"/>
       <c r="E48" s="130"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="18"/>
       <c r="C60" s="20"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -2252,25 +2269,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="104" t="s">
         <v>55</v>
       </c>
@@ -2286,12 +2303,12 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="70">
-        <v>687632.45000000007</v>
+        <v>520227.48</v>
       </c>
       <c r="L1" s="70"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de MAYO</v>
@@ -2311,7 +2328,7 @@
       <c r="L2" s="112"/>
       <c r="M2" s="75"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2352,7 +2369,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2386,7 +2403,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2398,11 +2415,11 @@
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="40">
-        <v>195131.99656</v>
+        <v>143100</v>
       </c>
       <c r="F5" s="79">
         <f>E5</f>
-        <v>195131.99656</v>
+        <v>143100</v>
       </c>
       <c r="G5" s="66">
         <f>E5-F5</f>
@@ -2417,7 +2434,7 @@
       </c>
       <c r="J5" s="37">
         <f>K$1/5</f>
-        <v>137526.49000000002</v>
+        <v>104045.496</v>
       </c>
       <c r="K5" s="115">
         <f>K2*D5</f>
@@ -2425,14 +2442,14 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>137526.49000000002</v>
+        <v>104045.496</v>
       </c>
       <c r="M5" s="38">
         <f>L5*4%+L5</f>
-        <v>143027.54960000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>108207.31584</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2444,14 +2461,15 @@
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="40">
-        <v>79762.493999999992</v>
+        <v>137288.984</v>
       </c>
       <c r="F6" s="79">
-        <v>80000</v>
+        <f>E6</f>
+        <v>137288.984</v>
       </c>
       <c r="G6" s="66">
         <f>E6-F6</f>
-        <v>-237.5060000000085</v>
+        <v>0</v>
       </c>
       <c r="H6" s="69">
         <f t="shared" ref="H6:H9" si="0">IF(G6&gt;0,G6*4%,0)</f>
@@ -2462,7 +2480,7 @@
       </c>
       <c r="J6" s="37">
         <f t="shared" ref="J6:J9" si="1">K$1/5</f>
-        <v>137526.49000000002</v>
+        <v>104045.496</v>
       </c>
       <c r="K6" s="115">
         <f>K2*D6</f>
@@ -2470,14 +2488,14 @@
       </c>
       <c r="L6" s="15">
         <f>J6+K6+H6+G6</f>
-        <v>137288.984</v>
+        <v>104045.496</v>
       </c>
       <c r="M6" s="38">
         <f t="shared" ref="M6:M9" si="2">L6*4%+L6</f>
-        <v>142780.54336000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>108207.31584</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2489,26 +2507,25 @@
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="40">
-        <v>195131.99656</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="F7" s="79">
-        <f>E7</f>
-        <v>195131.99656</v>
+        <v>0</v>
       </c>
       <c r="G7" s="66">
         <f t="shared" ref="G7:G8" si="3">E7-F7</f>
-        <v>0</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="H7" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5501.0596000000005</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="37">
         <f t="shared" si="1"/>
-        <v>137526.49000000002</v>
+        <v>104045.496</v>
       </c>
       <c r="K7" s="115">
         <f>K2*D7</f>
@@ -2516,14 +2533,14 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>137526.49000000002</v>
+        <v>247073.04560000001</v>
       </c>
       <c r="M7" s="38">
         <f t="shared" si="2"/>
-        <v>143027.54960000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>256955.967424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2531,30 +2548,29 @@
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="40">
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="F8" s="79">
-        <f>E8</f>
-        <v>79762.493999999992</v>
+        <v>0</v>
       </c>
       <c r="G8" s="66">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="H8" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5501.0596000000005</v>
       </c>
       <c r="I8" s="15">
         <v>0</v>
       </c>
       <c r="J8" s="37">
         <f t="shared" si="1"/>
-        <v>137526.49000000002</v>
+        <v>104045.496</v>
       </c>
       <c r="K8" s="115">
         <f>K2*D8</f>
@@ -2562,14 +2578,14 @@
       </c>
       <c r="L8" s="15">
         <f>J8+K8+H8+G8</f>
-        <v>137526.49000000002</v>
+        <v>247073.04560000001</v>
       </c>
       <c r="M8" s="38">
         <f t="shared" si="2"/>
-        <v>143027.54960000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>256955.967424</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2581,11 +2597,11 @@
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="40">
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="F9" s="79">
         <f>E9</f>
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="G9" s="66">
         <f>E9-F9</f>
@@ -2600,7 +2616,7 @@
       </c>
       <c r="J9" s="37">
         <f t="shared" si="1"/>
-        <v>137526.49000000002</v>
+        <v>104045.496</v>
       </c>
       <c r="K9" s="115">
         <f>K2*D9</f>
@@ -2608,14 +2624,14 @@
       </c>
       <c r="L9" s="15">
         <f>J9+K9+H9+G9</f>
-        <v>137526.49000000002</v>
+        <v>104045.496</v>
       </c>
       <c r="M9" s="38">
         <f t="shared" si="2"/>
-        <v>143027.54960000003</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>108207.31584</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2627,19 +2643,19 @@
       </c>
       <c r="E10" s="41">
         <f t="shared" si="4"/>
-        <v>629551.47511999996</v>
+        <v>692968.45400000003</v>
       </c>
       <c r="F10" s="41">
         <f>SUM(F5:F9)</f>
-        <v>629788.98111999989</v>
+        <v>417915.47400000005</v>
       </c>
       <c r="G10" s="49">
         <f t="shared" si="4"/>
-        <v>-237.5060000000085</v>
+        <v>275052.98000000004</v>
       </c>
       <c r="H10" s="49">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>11002.119200000001</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="4"/>
@@ -2647,7 +2663,7 @@
       </c>
       <c r="J10" s="45">
         <f t="shared" si="4"/>
-        <v>687632.45000000007</v>
+        <v>520227.48</v>
       </c>
       <c r="K10" s="45">
         <f t="shared" si="4"/>
@@ -2655,14 +2671,14 @@
       </c>
       <c r="L10" s="116">
         <f t="shared" si="4"/>
-        <v>687394.94400000002</v>
+        <v>806282.57920000004</v>
       </c>
       <c r="M10" s="116">
         <f t="shared" si="4"/>
-        <v>714890.74176000012</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>838533.88236799999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="133"/>
       <c r="B11" s="133"/>
       <c r="C11" s="133"/>
@@ -2677,10 +2693,10 @@
       <c r="L11" s="133"/>
       <c r="M11" s="133"/>
     </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C13" s="134"/>
       <c r="D13" s="134"/>
       <c r="E13" s="134"/>
@@ -2692,7 +2708,7 @@
       <c r="K13" s="134"/>
       <c r="L13" s="134"/>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C14" s="134"/>
       <c r="D14" s="134"/>
       <c r="E14" s="134"/>
@@ -2704,7 +2720,7 @@
       <c r="K14" s="134"/>
       <c r="L14" s="134"/>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C15" s="134"/>
       <c r="D15" s="134"/>
       <c r="E15" s="134"/>
@@ -2716,7 +2732,7 @@
       <c r="K15" s="134"/>
       <c r="L15" s="134"/>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C16" s="134"/>
       <c r="D16" s="134"/>
       <c r="E16" s="134"/>
@@ -2742,12 +2758,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="140" t="s">
         <v>24</v>
       </c>
@@ -2758,7 +2774,7 @@
       <c r="F1" s="87"/>
       <c r="G1" s="87"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="143" t="s">
         <v>50</v>
       </c>
@@ -2771,7 +2787,7 @@
       <c r="F2" s="88"/>
       <c r="G2" s="88"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="148" t="s">
         <v>0</v>
       </c>
@@ -2794,7 +2810,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="149"/>
       <c r="B4" s="149"/>
       <c r="C4" s="149"/>
@@ -2803,7 +2819,7 @@
       <c r="F4" s="136"/>
       <c r="G4" s="136"/>
     </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="89">
         <v>1</v>
       </c>
@@ -2826,7 +2842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="89">
         <v>2</v>
       </c>
@@ -2849,7 +2865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="89">
         <v>3</v>
       </c>
@@ -2872,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="89">
         <v>4</v>
       </c>
@@ -2895,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="89">
         <v>5</v>
       </c>
@@ -2918,7 +2934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="94">
         <v>6</v>
       </c>
@@ -2941,7 +2957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="99" t="s">
         <v>8</v>
       </c>
@@ -2960,7 +2976,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="137"/>
       <c r="B12" s="138"/>
       <c r="C12" s="138"/>
